--- a/ro_workstation/data/mis/archive/20260430.xlsx
+++ b/ro_workstation/data/mis/archive/20260430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Daily_MIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526A2B5C-1B09-44C4-93A3-7C0FF50A880C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F89CCF9-AE05-4136-9F77-2A2DA9AAE7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,13 +209,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,6 +500,9 @@
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AM57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="20" max="20" width="14.7109375" style="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -678,7 +682,7 @@
         <v>6.1338481999999993E-2</v>
       </c>
       <c r="T2" s="4">
-        <v>30.199661465999998</v>
+        <v>45.58421019</v>
       </c>
       <c r="U2" s="4">
         <v>117.60245392699998</v>
@@ -797,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="3">
-        <v>62.945657499999996</v>
+        <v>111.10028630000001</v>
       </c>
       <c r="U3" s="3">
         <v>612.27297120000003</v>
@@ -916,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="3">
-        <v>17.396445199999999</v>
+        <v>21.843721100000003</v>
       </c>
       <c r="U4" s="3">
         <v>126.38591260000001</v>
@@ -1035,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="3">
-        <v>37.093529300000007</v>
+        <v>71.161327600000007</v>
       </c>
       <c r="U5" s="3">
         <v>164.67250040000002</v>
@@ -1154,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>63.937250200000008</v>
+        <v>74.905570200000057</v>
       </c>
       <c r="U6" s="3">
         <v>384.85408060000003</v>
@@ -1273,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="T7" s="3">
-        <v>1.5266200000000001</v>
+        <v>19.42721049999999</v>
       </c>
       <c r="U7" s="3">
         <v>153.77285499999999</v>
@@ -1392,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>63.534807199999996</v>
+        <v>73.438046199999974</v>
       </c>
       <c r="U8" s="3">
         <v>155.9056334</v>
@@ -1511,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>259.29761209999998</v>
+        <v>307.3673426000002</v>
       </c>
       <c r="U9" s="3">
         <v>561.89952220000009</v>
@@ -1630,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="3">
-        <v>818.98209540000005</v>
+        <v>1599.8849104000001</v>
       </c>
       <c r="U10" s="3">
         <v>1618.7625016000002</v>
@@ -1749,7 +1753,7 @@
         <v>0.82447809999999999</v>
       </c>
       <c r="T11" s="3">
-        <v>1.6177440000000001</v>
+        <v>43.600389499999999</v>
       </c>
       <c r="U11" s="3">
         <v>225.69373380000002</v>
@@ -1868,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="3">
-        <v>24.9677355</v>
+        <v>32.701898499999906</v>
       </c>
       <c r="U12" s="3">
         <v>1112.9013488000001</v>
@@ -1987,7 +1991,7 @@
         <v>0.68941249999999998</v>
       </c>
       <c r="T13" s="3">
-        <v>19.6281523</v>
+        <v>32.259880599999995</v>
       </c>
       <c r="U13" s="3">
         <v>108.8948128</v>
@@ -2106,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
-        <v>49.957651000000006</v>
+        <v>54.615307699999981</v>
       </c>
       <c r="U14" s="3">
         <v>101.66356689999998</v>
@@ -2225,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="3">
-        <v>101.30398859999998</v>
+        <v>117.77187859999997</v>
       </c>
       <c r="U15" s="3">
         <v>294.48206389999996</v>
@@ -2344,7 +2348,7 @@
         <v>1.5839730999999999</v>
       </c>
       <c r="T16" s="3">
-        <v>33.342173099999997</v>
+        <v>49.178988699999998</v>
       </c>
       <c r="U16" s="3">
         <v>419.95940010000004</v>
@@ -2463,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="3">
-        <v>43.809374599999998</v>
+        <v>63.042059200000004</v>
       </c>
       <c r="U17" s="3">
         <v>189.99999350000002</v>
@@ -2582,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="3">
-        <v>6.4124252000000004</v>
+        <v>29.092963999999998</v>
       </c>
       <c r="U18" s="3">
         <v>69.420965100000004</v>
@@ -2701,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="3">
-        <v>53.448367300000001</v>
+        <v>105.86702949999992</v>
       </c>
       <c r="U19" s="3">
         <v>697.38170669999988</v>
@@ -2820,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>56.710138000000001</v>
+        <v>67.2236391</v>
       </c>
       <c r="U20" s="3">
         <v>165.40064810000001</v>
@@ -2939,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="3">
-        <v>55.043320899999991</v>
+        <v>59.011867100000011</v>
       </c>
       <c r="U21" s="3">
         <v>183.89094420000001</v>
@@ -3058,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
-        <v>49.039841100000011</v>
+        <v>70.191166399999986</v>
       </c>
       <c r="U22" s="3">
         <v>181.46336909999999</v>
@@ -3177,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="T23" s="3">
-        <v>22.929339499999998</v>
+        <v>50.63883109999999</v>
       </c>
       <c r="U23" s="3">
         <v>96.519192299999986</v>
@@ -3296,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
-        <v>22.120733300000001</v>
+        <v>35.525790399999963</v>
       </c>
       <c r="U24" s="3">
         <v>152.33037379999999</v>
@@ -3415,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="T25" s="3">
-        <v>32.694842100000002</v>
+        <v>33.421161100000013</v>
       </c>
       <c r="U25" s="3">
         <v>43.722035500000011</v>
@@ -3534,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="3">
-        <v>20.9182445</v>
+        <v>46.168244500000014</v>
       </c>
       <c r="U26" s="3">
         <v>83.460286000000011</v>
@@ -3653,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="3">
-        <v>73.634678100000002</v>
+        <v>90.17591809999999</v>
       </c>
       <c r="U27" s="3">
         <v>143.1194562</v>
@@ -3772,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="3">
-        <v>25.378590700000004</v>
+        <v>34.644354700000029</v>
       </c>
       <c r="U28" s="3">
         <v>244.45910160000005</v>
@@ -3891,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
-        <v>7.4725744999999995</v>
+        <v>18.154916500000002</v>
       </c>
       <c r="U29" s="3">
         <v>104.525446</v>
@@ -4010,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="3">
-        <v>16.0043471</v>
+        <v>17.857122500000013</v>
       </c>
       <c r="U30" s="3">
         <v>79.635850500000018</v>
@@ -4129,7 +4133,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="3">
-        <v>23.6484928</v>
+        <v>63.061402299999997</v>
       </c>
       <c r="U31" s="3">
         <v>123.8149282</v>
@@ -4248,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>9.774636000000001</v>
+        <v>19.627269600000002</v>
       </c>
       <c r="U32" s="3">
         <v>98.770209099999988</v>
@@ -4367,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="3">
-        <v>41.488124499999998</v>
+        <v>97.472505400000003</v>
       </c>
       <c r="U33" s="3">
         <v>97.472505400000003</v>
@@ -4486,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="3">
-        <v>51.756441800000005</v>
+        <v>68.681493500000002</v>
       </c>
       <c r="U34" s="3">
         <v>107.88236430000001</v>
@@ -4605,7 +4609,7 @@
         <v>0.92540669999999992</v>
       </c>
       <c r="T35" s="3">
-        <v>12.4214401</v>
+        <v>14.089662000000015</v>
       </c>
       <c r="U35" s="3">
         <v>306.38755739999999</v>
@@ -4724,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="3">
-        <v>46.551678600000002</v>
+        <v>46.611982700000027</v>
       </c>
       <c r="U36" s="3">
         <v>197.97256410000003</v>
@@ -4843,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="3">
-        <v>83.707981800000013</v>
+        <v>88.605430100000021</v>
       </c>
       <c r="U37" s="3">
         <v>109.97716060000002</v>
@@ -4962,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="3">
-        <v>23.044059799999996</v>
+        <v>32.970530799999999</v>
       </c>
       <c r="U38" s="3">
         <v>96.008276699999996</v>
@@ -5081,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="T39" s="3">
-        <v>19.014087200000002</v>
+        <v>28.04164949999997</v>
       </c>
       <c r="U39" s="3">
         <v>325.34318719999999</v>
@@ -5200,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="3">
-        <v>7.9699315999999989</v>
+        <v>12.669931600000002</v>
       </c>
       <c r="U40" s="3">
         <v>44.780558900000003</v>
@@ -5438,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="3">
-        <v>30.197088899999997</v>
+        <v>30.197088900000004</v>
       </c>
       <c r="U42" s="3">
         <v>65.762124299999996</v>
@@ -5557,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
-        <v>6.7354319</v>
+        <v>10.372974299999999</v>
       </c>
       <c r="U43" s="3">
         <v>44.313238500000004</v>
@@ -5676,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="3">
-        <v>21.036556100000002</v>
+        <v>21.816222000000021</v>
       </c>
       <c r="U44" s="3">
         <v>97.210346800000025</v>
@@ -5914,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="3">
-        <v>39.472929000000001</v>
+        <v>40.672928999999989</v>
       </c>
       <c r="U46" s="3">
         <v>93.493755699999994</v>
@@ -6033,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="3">
-        <v>41.676155200000004</v>
+        <v>41.676155199999968</v>
       </c>
       <c r="U47" s="3">
         <v>191.85981529999998</v>
@@ -6152,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="3">
-        <v>15.2618274</v>
+        <v>15.261827399999998</v>
       </c>
       <c r="U48" s="3">
         <v>50.318053299999995</v>
@@ -6271,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="T49" s="3">
-        <v>14.866251</v>
+        <v>74.676250999999993</v>
       </c>
       <c r="U49" s="3">
         <v>139.73524520000001</v>
@@ -6390,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="T50" s="3">
-        <v>32.778273299999995</v>
+        <v>32.778273300000002</v>
       </c>
       <c r="U50" s="3">
         <v>41.658012800000002</v>
@@ -6509,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="T51" s="3">
-        <v>29.687988999999998</v>
+        <v>29.687989000000016</v>
       </c>
       <c r="U51" s="3">
         <v>61.601798400000007</v>
@@ -6628,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="T52" s="3">
-        <v>8.0512180000000004</v>
+        <v>17.201218000000001</v>
       </c>
       <c r="U52" s="3">
         <v>21.532938000000001</v>
@@ -6747,7 +6751,7 @@
         <v>2.1105777999999997</v>
       </c>
       <c r="T53" s="3">
-        <v>134.2962417</v>
+        <v>134.29624169999997</v>
       </c>
       <c r="U53" s="3">
         <v>284.27187319999996</v>
@@ -6866,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="T54" s="3">
-        <v>79.709548499999983</v>
+        <v>93.058081500000029</v>
       </c>
       <c r="U54" s="3">
         <v>193.89107770000004</v>
@@ -6985,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="3">
-        <v>59.8245194</v>
+        <v>68.775122799999963</v>
       </c>
       <c r="U55" s="3">
         <v>289.00910339999996</v>

--- a/ro_workstation/data/mis/archive/20260430.xlsx
+++ b/ro_workstation/data/mis/archive/20260430.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Daily_MIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F89CCF9-AE05-4136-9F77-2A2DA9AAE7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -152,7 +152,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,8 +161,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1" tint="4.9989318521683403E-2"/>
+      <color theme="1" tint="0.0499899983406067"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -192,37 +198,130 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -496,15 +595,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AM57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="20" max="20" width="14.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7142857142857" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -623,7 +722,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="15">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -679,7 +778,7 @@
         <v>18.303714811999996</v>
       </c>
       <c r="S2" s="4">
-        <v>6.1338481999999993E-2</v>
+        <v>0.061338481999999993</v>
       </c>
       <c r="T2" s="4">
         <v>45.58421019</v>
@@ -742,7 +841,7 @@
         <v>0.26306380000000007</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="15">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -822,7 +921,7 @@
         <v>11641.513761100001</v>
       </c>
       <c r="AA3" s="1">
-        <v>21.1</v>
+        <v>21.100000000000001</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
@@ -831,16 +930,16 @@
         <v>0</v>
       </c>
       <c r="AD3" s="1">
-        <v>21.06</v>
+        <v>21.059999999999999</v>
       </c>
       <c r="AE3" s="1">
-        <v>42.16</v>
+        <v>42.159999999999997</v>
       </c>
       <c r="AF3" s="1">
         <v>87</v>
       </c>
       <c r="AG3" s="1">
-        <v>-44.84</v>
+        <v>-44.840000000000003</v>
       </c>
       <c r="AH3" s="1">
         <v>0</v>
@@ -861,7 +960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" ht="15">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -980,7 +1079,7 @@
         <v>0.62792000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" ht="15">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1060,7 +1159,7 @@
         <v>9288.1529136999998</v>
       </c>
       <c r="AA5" s="1">
-        <v>63.56</v>
+        <v>63.560000000000002</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
@@ -1072,13 +1171,13 @@
         <v>14.08</v>
       </c>
       <c r="AE5" s="1">
-        <v>77.64</v>
+        <v>77.640000000000001</v>
       </c>
       <c r="AF5" s="1">
         <v>45</v>
       </c>
       <c r="AG5" s="1">
-        <v>32.64</v>
+        <v>32.640000000000001</v>
       </c>
       <c r="AH5" s="1">
         <v>0</v>
@@ -1099,7 +1198,7 @@
         <v>0.4798</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" ht="15">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1191,7 +1290,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="AE6" s="1">
-        <v>60.17</v>
+        <v>60.170000000000002</v>
       </c>
       <c r="AF6" s="1">
         <v>50</v>
@@ -1206,7 +1305,7 @@
         <v>38.089697800000003</v>
       </c>
       <c r="AJ6" s="1">
-        <v>8.8929999999999995E-2</v>
+        <v>0.088929999999999995</v>
       </c>
       <c r="AK6" s="1">
         <v>0</v>
@@ -1215,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="AM6" s="1">
-        <v>8.8929999999999995E-2</v>
+        <v>0.088929999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="15">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1298,7 +1397,7 @@
         <v>6439.0842477000006</v>
       </c>
       <c r="AA7" s="1">
-        <v>47.42</v>
+        <v>47.420000000000002</v>
       </c>
       <c r="AB7" s="1">
         <v>0</v>
@@ -1310,13 +1409,13 @@
         <v>9.3800000000000008</v>
       </c>
       <c r="AE7" s="1">
-        <v>56.8</v>
+        <v>56.799999999999997</v>
       </c>
       <c r="AF7" s="1">
         <v>45</v>
       </c>
       <c r="AG7" s="1">
-        <v>11.8</v>
+        <v>11.800000000000001</v>
       </c>
       <c r="AH7" s="1">
         <v>0</v>
@@ -1325,7 +1424,7 @@
         <v>25.269869700000001</v>
       </c>
       <c r="AJ7" s="1">
-        <v>6.9999999999999994E-5</v>
+        <v>6.9999999999999994E-05</v>
       </c>
       <c r="AK7" s="1">
         <v>0</v>
@@ -1334,10 +1433,10 @@
         <v>0</v>
       </c>
       <c r="AM7" s="1">
-        <v>6.9999999999999994E-5</v>
+        <v>6.9999999999999994E-05</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" ht="15">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1426,16 +1525,16 @@
         <v>0</v>
       </c>
       <c r="AD8" s="1">
-        <v>5.56</v>
+        <v>5.5599999999999996</v>
       </c>
       <c r="AE8" s="1">
-        <v>23.47</v>
+        <v>23.469999999999999</v>
       </c>
       <c r="AF8" s="1">
         <v>35</v>
       </c>
       <c r="AG8" s="1">
-        <v>-11.53</v>
+        <v>-11.529999999999999</v>
       </c>
       <c r="AH8" s="1">
         <v>0</v>
@@ -1444,7 +1543,7 @@
         <v>24.146464099999999</v>
       </c>
       <c r="AJ8" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.0000000000000001E-05</v>
       </c>
       <c r="AK8" s="1">
         <v>0</v>
@@ -1453,10 +1552,10 @@
         <v>0</v>
       </c>
       <c r="AM8" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.0000000000000001E-05</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" ht="15">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1536,7 +1635,7 @@
         <v>8310.5261639</v>
       </c>
       <c r="AA9" s="1">
-        <v>42.69</v>
+        <v>42.689999999999998</v>
       </c>
       <c r="AB9" s="1">
         <v>0</v>
@@ -1548,13 +1647,13 @@
         <v>0</v>
       </c>
       <c r="AE9" s="1">
-        <v>42.69</v>
+        <v>42.689999999999998</v>
       </c>
       <c r="AF9" s="1">
         <v>40</v>
       </c>
       <c r="AG9" s="1">
-        <v>2.69</v>
+        <v>2.6899999999999999</v>
       </c>
       <c r="AH9" s="1">
         <v>0</v>
@@ -1563,7 +1662,7 @@
         <v>32.6734212</v>
       </c>
       <c r="AJ9" s="1">
-        <v>1.405E-2</v>
+        <v>0.01405</v>
       </c>
       <c r="AK9" s="1">
         <v>0</v>
@@ -1572,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="AM9" s="1">
-        <v>1.405E-2</v>
+        <v>0.01405</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" ht="15">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1655,10 +1754,10 @@
         <v>15687.710543399999</v>
       </c>
       <c r="AA10" s="1">
-        <v>90.73</v>
+        <v>90.730000000000004</v>
       </c>
       <c r="AB10" s="1">
-        <v>16.96</v>
+        <v>16.960000000000001</v>
       </c>
       <c r="AC10" s="1">
         <v>0</v>
@@ -1673,7 +1772,7 @@
         <v>80</v>
       </c>
       <c r="AG10" s="1">
-        <v>45.61</v>
+        <v>45.609999999999999</v>
       </c>
       <c r="AH10" s="1">
         <v>0</v>
@@ -1694,7 +1793,7 @@
         <v>20.72561</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" ht="15">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1783,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="1">
-        <v>22.06</v>
+        <v>22.059999999999999</v>
       </c>
       <c r="AE11" s="1">
         <v>231.59</v>
@@ -1813,7 +1912,7 @@
         <v>1.4043399999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" ht="15">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1893,7 +1992,7 @@
         <v>7978.9320782999994</v>
       </c>
       <c r="AA12" s="1">
-        <v>31.33</v>
+        <v>31.329999999999998</v>
       </c>
       <c r="AB12" s="1">
         <v>0</v>
@@ -1902,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="1">
-        <v>8.85</v>
+        <v>8.8499999999999996</v>
       </c>
       <c r="AE12" s="1">
         <v>40.18</v>
@@ -1911,7 +2010,7 @@
         <v>35</v>
       </c>
       <c r="AG12" s="1">
-        <v>5.18</v>
+        <v>5.1799999999999997</v>
       </c>
       <c r="AH12" s="1">
         <v>0</v>
@@ -1932,7 +2031,7 @@
         <v>2.18662</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" ht="15">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -2021,16 +2120,16 @@
         <v>0</v>
       </c>
       <c r="AD13" s="1">
-        <v>14.54</v>
+        <v>14.539999999999999</v>
       </c>
       <c r="AE13" s="1">
-        <v>46.7</v>
+        <v>46.700000000000003</v>
       </c>
       <c r="AF13" s="1">
         <v>30</v>
       </c>
       <c r="AG13" s="1">
-        <v>16.7</v>
+        <v>16.699999999999999</v>
       </c>
       <c r="AH13" s="1">
         <v>0</v>
@@ -2039,7 +2138,7 @@
         <v>18.488796600000001</v>
       </c>
       <c r="AJ13" s="1">
-        <v>9.6000000000000002E-4</v>
+        <v>0.00096000000000000002</v>
       </c>
       <c r="AK13" s="1">
         <v>0</v>
@@ -2048,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="AM13" s="1">
-        <v>9.6000000000000002E-4</v>
+        <v>0.00096000000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" ht="15">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -2131,10 +2230,10 @@
         <v>4221.7028667000004</v>
       </c>
       <c r="AA14" s="1">
-        <v>21.04</v>
+        <v>21.039999999999999</v>
       </c>
       <c r="AB14" s="1">
-        <v>9.35</v>
+        <v>9.3499999999999996</v>
       </c>
       <c r="AC14" s="1">
         <v>0</v>
@@ -2143,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="AE14" s="1">
-        <v>30.39</v>
+        <v>30.390000000000001</v>
       </c>
       <c r="AF14" s="1">
         <v>30</v>
       </c>
       <c r="AG14" s="1">
-        <v>0.39</v>
+        <v>0.39000000000000001</v>
       </c>
       <c r="AH14" s="1">
         <v>0</v>
@@ -2158,7 +2257,7 @@
         <v>15.867456799999999</v>
       </c>
       <c r="AJ14" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK14" s="1">
         <v>0</v>
@@ -2167,10 +2266,10 @@
         <v>0</v>
       </c>
       <c r="AM14" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" ht="15">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -2259,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="1">
-        <v>5.83</v>
+        <v>5.8300000000000001</v>
       </c>
       <c r="AE15" s="1">
         <v>18.579999999999998</v>
@@ -2277,7 +2376,7 @@
         <v>20.4304354</v>
       </c>
       <c r="AJ15" s="1">
-        <v>8.1999999999999998E-4</v>
+        <v>0.00081999999999999998</v>
       </c>
       <c r="AK15" s="1">
         <v>0</v>
@@ -2286,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="AM15" s="1">
-        <v>8.1999999999999998E-4</v>
+        <v>0.00081999999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" ht="15">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -2381,7 +2480,7 @@
         <v>4.1900000000000004</v>
       </c>
       <c r="AE16" s="1">
-        <v>21.26</v>
+        <v>21.260000000000002</v>
       </c>
       <c r="AF16" s="1">
         <v>33</v>
@@ -2408,7 +2507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2488,7 +2587,7 @@
         <v>9697.1971487999999</v>
       </c>
       <c r="AA17" s="1">
-        <v>46.98</v>
+        <v>46.979999999999997</v>
       </c>
       <c r="AB17" s="1">
         <v>0</v>
@@ -2497,10 +2596,10 @@
         <v>0</v>
       </c>
       <c r="AD17" s="1">
-        <v>7.6</v>
+        <v>7.5999999999999996</v>
       </c>
       <c r="AE17" s="1">
-        <v>54.58</v>
+        <v>54.579999999999998</v>
       </c>
       <c r="AF17" s="1">
         <v>35</v>
@@ -2527,7 +2626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2625,7 +2724,7 @@
         <v>25</v>
       </c>
       <c r="AG18" s="1">
-        <v>-5.66</v>
+        <v>-5.6600000000000001</v>
       </c>
       <c r="AH18" s="1">
         <v>0</v>
@@ -2634,7 +2733,7 @@
         <v>13.792566000000001</v>
       </c>
       <c r="AJ18" s="1">
-        <v>9.2000000000000003E-4</v>
+        <v>0.00092000000000000003</v>
       </c>
       <c r="AK18" s="1">
         <v>0</v>
@@ -2643,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="AM18" s="1">
-        <v>9.2000000000000003E-4</v>
+        <v>0.00092000000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2726,7 +2825,7 @@
         <v>4893.6609725999997</v>
       </c>
       <c r="AA19" s="1">
-        <v>7.59</v>
+        <v>7.5899999999999999</v>
       </c>
       <c r="AB19" s="1">
         <v>0</v>
@@ -2738,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="AE19" s="1">
-        <v>7.59</v>
+        <v>7.5899999999999999</v>
       </c>
       <c r="AF19" s="1">
         <v>25</v>
@@ -2753,7 +2852,7 @@
         <v>17.806537500000001</v>
       </c>
       <c r="AJ19" s="1">
-        <v>3.6000000000000002E-4</v>
+        <v>0.00036000000000000002</v>
       </c>
       <c r="AK19" s="1">
         <v>0</v>
@@ -2762,10 +2861,10 @@
         <v>0</v>
       </c>
       <c r="AM19" s="1">
-        <v>3.6000000000000002E-4</v>
+        <v>0.00036000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2845,7 +2944,7 @@
         <v>7077.9855334999993</v>
       </c>
       <c r="AA20" s="1">
-        <v>17.72</v>
+        <v>17.719999999999999</v>
       </c>
       <c r="AB20" s="1">
         <v>0</v>
@@ -2857,13 +2956,13 @@
         <v>10.199999999999999</v>
       </c>
       <c r="AE20" s="1">
-        <v>27.92</v>
+        <v>27.920000000000002</v>
       </c>
       <c r="AF20" s="1">
         <v>30</v>
       </c>
       <c r="AG20" s="1">
-        <v>-2.08</v>
+        <v>-2.0800000000000001</v>
       </c>
       <c r="AH20" s="1">
         <v>0</v>
@@ -2884,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2973,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="1">
-        <v>6.94</v>
+        <v>6.9400000000000004</v>
       </c>
       <c r="AE21" s="1">
         <v>22.93</v>
@@ -2982,7 +3081,7 @@
         <v>30</v>
       </c>
       <c r="AG21" s="1">
-        <v>-7.07</v>
+        <v>-7.0700000000000003</v>
       </c>
       <c r="AH21" s="1">
         <v>0</v>
@@ -2991,7 +3090,7 @@
         <v>20.846316600000002</v>
       </c>
       <c r="AJ21" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK21" s="1">
         <v>0</v>
@@ -3000,10 +3099,10 @@
         <v>0</v>
       </c>
       <c r="AM21" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3083,7 +3182,7 @@
         <v>5570.2617295999999</v>
       </c>
       <c r="AA22" s="1">
-        <v>49.7</v>
+        <v>49.700000000000003</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -3092,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="1">
-        <v>10.3</v>
+        <v>10.300000000000001</v>
       </c>
       <c r="AE22" s="1">
         <v>60</v>
@@ -3110,7 +3209,7 @@
         <v>24.168362299999998</v>
       </c>
       <c r="AJ22" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK22" s="1">
         <v>0</v>
@@ -3119,10 +3218,10 @@
         <v>0</v>
       </c>
       <c r="AM22" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3205,16 +3304,16 @@
         <v>15.57</v>
       </c>
       <c r="AB23" s="1">
-        <v>7.93</v>
+        <v>7.9299999999999997</v>
       </c>
       <c r="AC23" s="1">
         <v>0</v>
       </c>
       <c r="AD23" s="1">
-        <v>30.85</v>
+        <v>30.850000000000001</v>
       </c>
       <c r="AE23" s="1">
-        <v>54.35</v>
+        <v>54.350000000000001</v>
       </c>
       <c r="AF23" s="1">
         <v>70</v>
@@ -3229,7 +3328,7 @@
         <v>32.711865899999999</v>
       </c>
       <c r="AJ23" s="1">
-        <v>9.0079999999999993E-2</v>
+        <v>0.090079999999999993</v>
       </c>
       <c r="AK23" s="1">
         <v>0</v>
@@ -3238,10 +3337,10 @@
         <v>0</v>
       </c>
       <c r="AM23" s="1">
-        <v>9.0079999999999993E-2</v>
+        <v>0.090079999999999993</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3333,13 +3432,13 @@
         <v>0</v>
       </c>
       <c r="AE24" s="1">
-        <v>54.67</v>
+        <v>54.670000000000002</v>
       </c>
       <c r="AF24" s="1">
         <v>45</v>
       </c>
       <c r="AG24" s="1">
-        <v>9.67</v>
+        <v>9.6699999999999999</v>
       </c>
       <c r="AH24" s="1">
         <v>0</v>
@@ -3348,7 +3447,7 @@
         <v>19.084721699999999</v>
       </c>
       <c r="AJ24" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>0.00055000000000000003</v>
       </c>
       <c r="AK24" s="1">
         <v>0</v>
@@ -3357,10 +3456,10 @@
         <v>0</v>
       </c>
       <c r="AM24" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>0.00055000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3449,16 +3548,16 @@
         <v>0</v>
       </c>
       <c r="AD25" s="1">
-        <v>10.8</v>
+        <v>10.800000000000001</v>
       </c>
       <c r="AE25" s="1">
-        <v>28.55</v>
+        <v>28.550000000000001</v>
       </c>
       <c r="AF25" s="1">
         <v>25</v>
       </c>
       <c r="AG25" s="1">
-        <v>3.55</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="AH25" s="1">
         <v>0</v>
@@ -3467,7 +3566,7 @@
         <v>10.291239900000001</v>
       </c>
       <c r="AJ25" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="AK25" s="1">
         <v>0</v>
@@ -3476,10 +3575,10 @@
         <v>0</v>
       </c>
       <c r="AM25" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>0.0030000000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3559,7 +3658,7 @@
         <v>8319.7598779</v>
       </c>
       <c r="AA26" s="1">
-        <v>9.9</v>
+        <v>9.9000000000000004</v>
       </c>
       <c r="AB26" s="1">
         <v>0</v>
@@ -3568,16 +3667,16 @@
         <v>0</v>
       </c>
       <c r="AD26" s="1">
-        <v>7.4</v>
+        <v>7.4000000000000004</v>
       </c>
       <c r="AE26" s="1">
-        <v>17.3</v>
+        <v>17.300000000000001</v>
       </c>
       <c r="AF26" s="1">
         <v>32</v>
       </c>
       <c r="AG26" s="1">
-        <v>-14.7</v>
+        <v>-14.699999999999999</v>
       </c>
       <c r="AH26" s="1">
         <v>0</v>
@@ -3598,7 +3697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3687,16 +3786,16 @@
         <v>0</v>
       </c>
       <c r="AD27" s="1">
-        <v>12.05</v>
+        <v>12.050000000000001</v>
       </c>
       <c r="AE27" s="1">
-        <v>37.39</v>
+        <v>37.390000000000001</v>
       </c>
       <c r="AF27" s="1">
         <v>36</v>
       </c>
       <c r="AG27" s="1">
-        <v>1.39</v>
+        <v>1.3899999999999999</v>
       </c>
       <c r="AH27" s="1">
         <v>0</v>
@@ -3705,7 +3804,7 @@
         <v>29.827856499999999</v>
       </c>
       <c r="AJ27" s="1">
-        <v>3.0499999999999999E-2</v>
+        <v>0.030499999999999999</v>
       </c>
       <c r="AK27" s="1">
         <v>0</v>
@@ -3714,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="AM27" s="1">
-        <v>3.0499999999999999E-2</v>
+        <v>0.030499999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3797,7 +3896,7 @@
         <v>6772.3666303</v>
       </c>
       <c r="AA28" s="1">
-        <v>30.29</v>
+        <v>30.289999999999999</v>
       </c>
       <c r="AB28" s="1">
         <v>0</v>
@@ -3809,13 +3908,13 @@
         <v>5.29</v>
       </c>
       <c r="AE28" s="1">
-        <v>35.58</v>
+        <v>35.579999999999998</v>
       </c>
       <c r="AF28" s="1">
         <v>30</v>
       </c>
       <c r="AG28" s="1">
-        <v>5.58</v>
+        <v>5.5800000000000001</v>
       </c>
       <c r="AH28" s="1">
         <v>0</v>
@@ -3824,7 +3923,7 @@
         <v>25.714044999999999</v>
       </c>
       <c r="AJ28" s="1">
-        <v>4.3800000000000002E-3</v>
+        <v>0.0043800000000000002</v>
       </c>
       <c r="AK28" s="1">
         <v>0</v>
@@ -3833,10 +3932,10 @@
         <v>0</v>
       </c>
       <c r="AM28" s="1">
-        <v>4.3800000000000002E-3</v>
+        <v>0.0043800000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3916,7 +4015,7 @@
         <v>8650.7009545000001</v>
       </c>
       <c r="AA29" s="1">
-        <v>63.99</v>
+        <v>63.990000000000002</v>
       </c>
       <c r="AB29" s="1">
         <v>12.99</v>
@@ -3925,16 +4024,16 @@
         <v>0</v>
       </c>
       <c r="AD29" s="1">
-        <v>5.99</v>
+        <v>5.9900000000000002</v>
       </c>
       <c r="AE29" s="1">
-        <v>82.97</v>
+        <v>82.969999999999999</v>
       </c>
       <c r="AF29" s="1">
         <v>40</v>
       </c>
       <c r="AG29" s="1">
-        <v>42.97</v>
+        <v>42.969999999999999</v>
       </c>
       <c r="AH29" s="1">
         <v>0</v>
@@ -3955,7 +4054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4035,7 +4134,7 @@
         <v>9492.2339716999995</v>
       </c>
       <c r="AA30" s="1">
-        <v>29.1</v>
+        <v>29.100000000000001</v>
       </c>
       <c r="AB30" s="1">
         <v>10.82</v>
@@ -4047,13 +4146,13 @@
         <v>0</v>
       </c>
       <c r="AE30" s="1">
-        <v>39.92</v>
+        <v>39.920000000000002</v>
       </c>
       <c r="AF30" s="1">
         <v>40</v>
       </c>
       <c r="AG30" s="1">
-        <v>-0.08</v>
+        <v>-0.080000000000000002</v>
       </c>
       <c r="AH30" s="1">
         <v>0</v>
@@ -4074,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4154,7 +4253,7 @@
         <v>7123.3173863000002</v>
       </c>
       <c r="AA31" s="1">
-        <v>41.9</v>
+        <v>41.899999999999999</v>
       </c>
       <c r="AB31" s="1">
         <v>0</v>
@@ -4163,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AD31" s="1">
-        <v>8.07</v>
+        <v>8.0700000000000003</v>
       </c>
       <c r="AE31" s="1">
-        <v>49.97</v>
+        <v>49.969999999999999</v>
       </c>
       <c r="AF31" s="1">
         <v>30</v>
       </c>
       <c r="AG31" s="1">
-        <v>19.97</v>
+        <v>19.969999999999999</v>
       </c>
       <c r="AH31" s="1">
         <v>0</v>
@@ -4181,7 +4280,7 @@
         <v>31.588827800000001</v>
       </c>
       <c r="AJ31" s="1">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AK31" s="1">
         <v>0</v>
@@ -4190,10 +4289,10 @@
         <v>0</v>
       </c>
       <c r="AM31" s="1">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4282,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="AD32" s="1">
-        <v>10.7</v>
+        <v>10.699999999999999</v>
       </c>
       <c r="AE32" s="1">
         <v>13.02</v>
@@ -4312,7 +4411,7 @@
         <v>0.50973000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="15">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4392,7 +4491,7 @@
         <v>13281.803226</v>
       </c>
       <c r="AA33" s="1">
-        <v>3.26</v>
+        <v>3.2599999999999998</v>
       </c>
       <c r="AB33" s="1">
         <v>0</v>
@@ -4404,13 +4503,13 @@
         <v>9.5399999999999991</v>
       </c>
       <c r="AE33" s="1">
-        <v>12.8</v>
+        <v>12.800000000000001</v>
       </c>
       <c r="AF33" s="1">
         <v>43</v>
       </c>
       <c r="AG33" s="1">
-        <v>-30.2</v>
+        <v>-30.199999999999999</v>
       </c>
       <c r="AH33" s="1">
         <v>0</v>
@@ -4419,7 +4518,7 @@
         <v>39.223950100000003</v>
       </c>
       <c r="AJ33" s="1">
-        <v>8.8999999999999995E-4</v>
+        <v>0.00088999999999999995</v>
       </c>
       <c r="AK33" s="1">
         <v>0</v>
@@ -4428,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="AM33" s="1">
-        <v>8.8999999999999995E-4</v>
+        <v>0.00088999999999999995</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="15">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4511,25 +4610,25 @@
         <v>8980.622594800001</v>
       </c>
       <c r="AA34" s="1">
-        <v>12.79</v>
+        <v>12.789999999999999</v>
       </c>
       <c r="AB34" s="1">
-        <v>11.63</v>
+        <v>11.630000000000001</v>
       </c>
       <c r="AC34" s="1">
         <v>0</v>
       </c>
       <c r="AD34" s="1">
-        <v>12.12</v>
+        <v>12.119999999999999</v>
       </c>
       <c r="AE34" s="1">
-        <v>36.54</v>
+        <v>36.539999999999999</v>
       </c>
       <c r="AF34" s="1">
         <v>55</v>
       </c>
       <c r="AG34" s="1">
-        <v>-18.46</v>
+        <v>-18.460000000000001</v>
       </c>
       <c r="AH34" s="1">
         <v>0</v>
@@ -4538,7 +4637,7 @@
         <v>38.953562300000002</v>
       </c>
       <c r="AJ34" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK34" s="1">
         <v>0</v>
@@ -4547,10 +4646,10 @@
         <v>0</v>
       </c>
       <c r="AM34" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="15">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4603,7 +4702,7 @@
         <v>288.2724887</v>
       </c>
       <c r="R35" s="3">
-        <v>3.1</v>
+        <v>3.1000000000000001</v>
       </c>
       <c r="S35" s="3">
         <v>0.92540669999999992</v>
@@ -4630,7 +4729,7 @@
         <v>7322.9218438000007</v>
       </c>
       <c r="AA35" s="1">
-        <v>9.68</v>
+        <v>9.6799999999999997</v>
       </c>
       <c r="AB35" s="1">
         <v>0</v>
@@ -4639,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="AD35" s="1">
-        <v>4.74</v>
+        <v>4.7400000000000002</v>
       </c>
       <c r="AE35" s="1">
         <v>14.42</v>
@@ -4669,7 +4768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="15">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4767,7 +4866,7 @@
         <v>33</v>
       </c>
       <c r="AG36" s="1">
-        <v>6.16</v>
+        <v>6.1600000000000001</v>
       </c>
       <c r="AH36" s="1">
         <v>0</v>
@@ -4776,7 +4875,7 @@
         <v>28.818360999999999</v>
       </c>
       <c r="AJ36" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK36" s="1">
         <v>0</v>
@@ -4785,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="AM36" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="15">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4880,13 +4979,13 @@
         <v>12.18</v>
       </c>
       <c r="AE37" s="1">
-        <v>51.11</v>
+        <v>51.109999999999999</v>
       </c>
       <c r="AF37" s="1">
         <v>34</v>
       </c>
       <c r="AG37" s="1">
-        <v>17.11</v>
+        <v>17.109999999999999</v>
       </c>
       <c r="AH37" s="1">
         <v>0</v>
@@ -4895,7 +4994,7 @@
         <v>40.719563000000001</v>
       </c>
       <c r="AJ37" s="1">
-        <v>1.546E-2</v>
+        <v>0.01546</v>
       </c>
       <c r="AK37" s="1">
         <v>0</v>
@@ -4904,10 +5003,10 @@
         <v>0</v>
       </c>
       <c r="AM37" s="1">
-        <v>1.546E-2</v>
+        <v>0.01546</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="15">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -4996,16 +5095,16 @@
         <v>0</v>
       </c>
       <c r="AD38" s="1">
-        <v>9.51</v>
+        <v>9.5099999999999998</v>
       </c>
       <c r="AE38" s="1">
-        <v>18.05</v>
+        <v>18.050000000000001</v>
       </c>
       <c r="AF38" s="1">
         <v>34</v>
       </c>
       <c r="AG38" s="1">
-        <v>-15.95</v>
+        <v>-15.949999999999999</v>
       </c>
       <c r="AH38" s="1">
         <v>0</v>
@@ -5014,7 +5113,7 @@
         <v>30.813776799999999</v>
       </c>
       <c r="AJ38" s="1">
-        <v>2.0920000000000001E-2</v>
+        <v>0.020920000000000001</v>
       </c>
       <c r="AK38" s="1">
         <v>0</v>
@@ -5023,10 +5122,10 @@
         <v>0</v>
       </c>
       <c r="AM38" s="1">
-        <v>2.0920000000000001E-2</v>
+        <v>0.020920000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="15">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -5106,7 +5205,7 @@
         <v>12746.1221971</v>
       </c>
       <c r="AA39" s="1">
-        <v>28.95</v>
+        <v>28.949999999999999</v>
       </c>
       <c r="AB39" s="1">
         <v>0</v>
@@ -5118,13 +5217,13 @@
         <v>14.6</v>
       </c>
       <c r="AE39" s="1">
-        <v>43.55</v>
+        <v>43.549999999999997</v>
       </c>
       <c r="AF39" s="1">
         <v>38</v>
       </c>
       <c r="AG39" s="1">
-        <v>5.55</v>
+        <v>5.5499999999999998</v>
       </c>
       <c r="AH39" s="1">
         <v>0</v>
@@ -5145,7 +5244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="15">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5225,7 +5324,7 @@
         <v>8817.9980976999996</v>
       </c>
       <c r="AA40" s="1">
-        <v>25.4</v>
+        <v>25.399999999999999</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
@@ -5234,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="AD40" s="1">
-        <v>7.47</v>
+        <v>7.4699999999999998</v>
       </c>
       <c r="AE40" s="1">
         <v>32.869999999999997</v>
@@ -5243,7 +5342,7 @@
         <v>35</v>
       </c>
       <c r="AG40" s="1">
-        <v>-2.13</v>
+        <v>-2.1299999999999999</v>
       </c>
       <c r="AH40" s="1">
         <v>0</v>
@@ -5252,7 +5351,7 @@
         <v>32.705116099999998</v>
       </c>
       <c r="AJ40" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK40" s="1">
         <v>0</v>
@@ -5261,10 +5360,10 @@
         <v>0</v>
       </c>
       <c r="AM40" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="15">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5353,16 +5452,16 @@
         <v>0</v>
       </c>
       <c r="AD41" s="1">
-        <v>6.89</v>
+        <v>6.8899999999999997</v>
       </c>
       <c r="AE41" s="1">
-        <v>30.39</v>
+        <v>30.390000000000001</v>
       </c>
       <c r="AF41" s="1">
         <v>33</v>
       </c>
       <c r="AG41" s="1">
-        <v>-2.61</v>
+        <v>-2.6099999999999999</v>
       </c>
       <c r="AH41" s="1">
         <v>0</v>
@@ -5371,7 +5470,7 @@
         <v>16.9863538</v>
       </c>
       <c r="AJ41" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK41" s="1">
         <v>0</v>
@@ -5380,10 +5479,10 @@
         <v>0</v>
       </c>
       <c r="AM41" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="15">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -5463,7 +5562,7 @@
         <v>6555.6377082999998</v>
       </c>
       <c r="AA42" s="1">
-        <v>23.85</v>
+        <v>23.850000000000001</v>
       </c>
       <c r="AB42" s="1">
         <v>19.16</v>
@@ -5475,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="AE42" s="1">
-        <v>43.01</v>
+        <v>43.009999999999998</v>
       </c>
       <c r="AF42" s="1">
         <v>34</v>
       </c>
       <c r="AG42" s="1">
-        <v>9.01</v>
+        <v>9.0099999999999998</v>
       </c>
       <c r="AH42" s="1">
         <v>0</v>
@@ -5502,7 +5601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="15">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5582,7 +5681,7 @@
         <v>11409.8332371</v>
       </c>
       <c r="AA43" s="1">
-        <v>15.37</v>
+        <v>15.369999999999999</v>
       </c>
       <c r="AB43" s="1">
         <v>0</v>
@@ -5591,16 +5690,16 @@
         <v>0</v>
       </c>
       <c r="AD43" s="1">
-        <v>6.85</v>
+        <v>6.8499999999999996</v>
       </c>
       <c r="AE43" s="1">
-        <v>22.22</v>
+        <v>22.219999999999999</v>
       </c>
       <c r="AF43" s="1">
         <v>30</v>
       </c>
       <c r="AG43" s="1">
-        <v>-7.78</v>
+        <v>-7.7800000000000002</v>
       </c>
       <c r="AH43" s="1">
         <v>0</v>
@@ -5621,7 +5720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="15">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5674,7 +5773,7 @@
         <v>72.594124800000003</v>
       </c>
       <c r="R44" s="3">
-        <v>2.8</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -5701,7 +5800,7 @@
         <v>4470.1409749000004</v>
       </c>
       <c r="AA44" s="1">
-        <v>6.98</v>
+        <v>6.9800000000000004</v>
       </c>
       <c r="AB44" s="1">
         <v>0</v>
@@ -5710,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="AD44" s="1">
-        <v>3.92</v>
+        <v>3.9199999999999999</v>
       </c>
       <c r="AE44" s="1">
         <v>10.9</v>
@@ -5728,7 +5827,7 @@
         <v>16.4205504</v>
       </c>
       <c r="AJ44" s="1">
-        <v>1.84E-2</v>
+        <v>0.0184</v>
       </c>
       <c r="AK44" s="1">
         <v>0</v>
@@ -5737,10 +5836,10 @@
         <v>0</v>
       </c>
       <c r="AM44" s="1">
-        <v>1.84E-2</v>
+        <v>0.0184</v>
       </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="15">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5820,7 +5919,7 @@
         <v>9853.2512330999998</v>
       </c>
       <c r="AA45" s="1">
-        <v>0.23</v>
+        <v>0.23000000000000001</v>
       </c>
       <c r="AB45" s="1">
         <v>0</v>
@@ -5832,13 +5931,13 @@
         <v>18.559999999999999</v>
       </c>
       <c r="AE45" s="1">
-        <v>18.79</v>
+        <v>18.789999999999999</v>
       </c>
       <c r="AF45" s="1">
         <v>40</v>
       </c>
       <c r="AG45" s="1">
-        <v>-21.21</v>
+        <v>-21.210000000000001</v>
       </c>
       <c r="AH45" s="1">
         <v>0</v>
@@ -5847,7 +5946,7 @@
         <v>40.076543899999997</v>
       </c>
       <c r="AJ45" s="1">
-        <v>1.6000000000000001E-4</v>
+        <v>0.00016000000000000001</v>
       </c>
       <c r="AK45" s="1">
         <v>0</v>
@@ -5856,10 +5955,10 @@
         <v>0</v>
       </c>
       <c r="AM45" s="1">
-        <v>1.6000000000000001E-4</v>
+        <v>0.00016000000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="15">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -5957,7 +6056,7 @@
         <v>33</v>
       </c>
       <c r="AG46" s="1">
-        <v>-4.82</v>
+        <v>-4.8200000000000003</v>
       </c>
       <c r="AH46" s="1">
         <v>0</v>
@@ -5978,7 +6077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="15">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -6058,7 +6157,7 @@
         <v>8643.9316048000001</v>
       </c>
       <c r="AA47" s="1">
-        <v>21.13</v>
+        <v>21.129999999999999</v>
       </c>
       <c r="AB47" s="1">
         <v>0</v>
@@ -6067,16 +6166,16 @@
         <v>0</v>
       </c>
       <c r="AD47" s="1">
-        <v>5.18</v>
+        <v>5.1799999999999997</v>
       </c>
       <c r="AE47" s="1">
-        <v>26.31</v>
+        <v>26.309999999999999</v>
       </c>
       <c r="AF47" s="1">
         <v>35</v>
       </c>
       <c r="AG47" s="1">
-        <v>-8.69</v>
+        <v>-8.6899999999999995</v>
       </c>
       <c r="AH47" s="1">
         <v>0</v>
@@ -6097,7 +6196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="15">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -6177,7 +6276,7 @@
         <v>8058.1517383000009</v>
       </c>
       <c r="AA48" s="1">
-        <v>20.67</v>
+        <v>20.670000000000002</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
@@ -6189,13 +6288,13 @@
         <v>4.8899999999999997</v>
       </c>
       <c r="AE48" s="1">
-        <v>25.56</v>
+        <v>25.559999999999999</v>
       </c>
       <c r="AF48" s="1">
         <v>27</v>
       </c>
       <c r="AG48" s="1">
-        <v>-1.44</v>
+        <v>-1.4399999999999999</v>
       </c>
       <c r="AH48" s="1">
         <v>0</v>
@@ -6204,7 +6303,7 @@
         <v>29.915070499999999</v>
       </c>
       <c r="AJ48" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK48" s="1">
         <v>0</v>
@@ -6213,10 +6312,10 @@
         <v>0</v>
       </c>
       <c r="AM48" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -6296,7 +6395,7 @@
         <v>4748.3504748999994</v>
       </c>
       <c r="AA49" s="1">
-        <v>22.29</v>
+        <v>22.289999999999999</v>
       </c>
       <c r="AB49" s="1">
         <v>0</v>
@@ -6308,7 +6407,7 @@
         <v>8.75</v>
       </c>
       <c r="AE49" s="1">
-        <v>31.04</v>
+        <v>31.039999999999999</v>
       </c>
       <c r="AF49" s="1">
         <v>27</v>
@@ -6335,7 +6434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -6424,16 +6523,16 @@
         <v>0</v>
       </c>
       <c r="AD50" s="1">
-        <v>5.78</v>
+        <v>5.7800000000000002</v>
       </c>
       <c r="AE50" s="1">
-        <v>28.28</v>
+        <v>28.280000000000001</v>
       </c>
       <c r="AF50" s="1">
         <v>15</v>
       </c>
       <c r="AG50" s="1">
-        <v>13.28</v>
+        <v>13.279999999999999</v>
       </c>
       <c r="AH50" s="1">
         <v>0</v>
@@ -6454,7 +6553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -6546,7 +6645,7 @@
         <v>8.0500000000000007</v>
       </c>
       <c r="AE51" s="1">
-        <v>40.17</v>
+        <v>40.170000000000002</v>
       </c>
       <c r="AF51" s="1">
         <v>25</v>
@@ -6573,7 +6672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -6653,7 +6752,7 @@
         <v>3002.8637263999999</v>
       </c>
       <c r="AA52" s="1">
-        <v>39.94</v>
+        <v>39.939999999999998</v>
       </c>
       <c r="AB52" s="1">
         <v>0</v>
@@ -6665,13 +6764,13 @@
         <v>13.59</v>
       </c>
       <c r="AE52" s="1">
-        <v>53.53</v>
+        <v>53.530000000000001</v>
       </c>
       <c r="AF52" s="1">
         <v>40</v>
       </c>
       <c r="AG52" s="1">
-        <v>13.53</v>
+        <v>13.529999999999999</v>
       </c>
       <c r="AH52" s="1">
         <v>0</v>
@@ -6680,7 +6779,7 @@
         <v>9.2287087000000003</v>
       </c>
       <c r="AJ52" s="1">
-        <v>3.32E-2</v>
+        <v>0.0332</v>
       </c>
       <c r="AK52" s="1">
         <v>0</v>
@@ -6689,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="AM52" s="1">
-        <v>3.32E-2</v>
+        <v>0.0332</v>
       </c>
     </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -6772,7 +6871,7 @@
         <v>6495.9707320999996</v>
       </c>
       <c r="AA53" s="1">
-        <v>30.05</v>
+        <v>30.050000000000001</v>
       </c>
       <c r="AB53" s="1">
         <v>0</v>
@@ -6781,16 +6880,16 @@
         <v>0</v>
       </c>
       <c r="AD53" s="1">
-        <v>7.14</v>
+        <v>7.1399999999999997</v>
       </c>
       <c r="AE53" s="1">
-        <v>37.19</v>
+        <v>37.189999999999998</v>
       </c>
       <c r="AF53" s="1">
         <v>28</v>
       </c>
       <c r="AG53" s="1">
-        <v>9.19</v>
+        <v>9.1899999999999995</v>
       </c>
       <c r="AH53" s="1">
         <v>0</v>
@@ -6811,7 +6910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6891,7 +6990,7 @@
         <v>6129.9357787999998</v>
       </c>
       <c r="AA54" s="1">
-        <v>20.79</v>
+        <v>20.789999999999999</v>
       </c>
       <c r="AB54" s="1">
         <v>0</v>
@@ -6903,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="AE54" s="1">
-        <v>20.79</v>
+        <v>20.789999999999999</v>
       </c>
       <c r="AF54" s="1">
         <v>23</v>
@@ -6930,7 +7029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -7019,7 +7118,7 @@
         <v>0</v>
       </c>
       <c r="AD55" s="1">
-        <v>0.98</v>
+        <v>0.97999999999999998</v>
       </c>
       <c r="AE55" s="1">
         <v>5.75</v>
@@ -7037,7 +7136,7 @@
         <v>19.957572500000001</v>
       </c>
       <c r="AJ55" s="1">
-        <v>4.3020000000000003E-2</v>
+        <v>0.043020000000000003</v>
       </c>
       <c r="AK55" s="1">
         <v>0</v>
@@ -7046,10 +7145,10 @@
         <v>0</v>
       </c>
       <c r="AM55" s="1">
-        <v>4.3020000000000003E-2</v>
+        <v>0.043020000000000003</v>
       </c>
     </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -7066,7 +7165,7 @@
         <v>982.65999319999992</v>
       </c>
       <c r="F56" s="3">
-        <v>83.45</v>
+        <v>83.450000000000003</v>
       </c>
       <c r="G56" s="3">
         <v>1070.1109331999999</v>
@@ -7102,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="R56" s="3">
-        <v>4.42</v>
+        <v>4.4199999999999999</v>
       </c>
       <c r="S56" s="3">
         <v>0</v>
@@ -7129,7 +7228,7 @@
         <v>1353.4217547000001</v>
       </c>
       <c r="AA56" s="1">
-        <v>23.3</v>
+        <v>23.300000000000001</v>
       </c>
       <c r="AB56" s="1">
         <v>0</v>
@@ -7141,19 +7240,19 @@
         <v>4.4800000000000004</v>
       </c>
       <c r="AE56" s="1">
-        <v>27.78</v>
+        <v>27.780000000000001</v>
       </c>
       <c r="AF56" s="1">
         <v>20</v>
       </c>
       <c r="AG56" s="1">
-        <v>7.78</v>
+        <v>7.7800000000000002</v>
       </c>
       <c r="AH56" s="1">
         <v>0</v>
       </c>
       <c r="AI56" s="1">
-        <v>-3.64429E-2</v>
+        <v>-0.0364429</v>
       </c>
       <c r="AJ56" s="1">
         <v>0</v>
@@ -7168,7 +7267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -7182,13 +7281,13 @@
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>72.09</v>
+        <v>72.090000000000003</v>
       </c>
       <c r="F57" s="1">
-        <v>14.63</v>
+        <v>14.630000000000001</v>
       </c>
       <c r="G57" s="1">
-        <v>86.72</v>
+        <v>86.719999999999999</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -7212,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="3">
-        <v>14.63</v>
+        <v>14.630000000000001</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -7245,7 +7344,7 @@
         <v>19.259999999999998</v>
       </c>
       <c r="Z57" s="3">
-        <v>86.72</v>
+        <v>86.719999999999999</v>
       </c>
       <c r="AA57" s="1">
         <v>0</v>
@@ -7289,5 +7388,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>